--- a/datasets/output/local_file__Dataset4_FirstWithOutl__single__20260505_162534.xlsx
+++ b/datasets/output/local_file__Dataset4_FirstWithOutl__single__20260505_162534.xlsx
@@ -498,7 +498,7 @@
         <v>4.258068237032394</v>
       </c>
       <c r="I2" t="n">
-        <v>765.1392</v>
+        <v>757.3325</v>
       </c>
     </row>
     <row r="3">
@@ -529,7 +529,7 @@
         <v>4.103762772073641</v>
       </c>
       <c r="I3" t="n">
-        <v>773.6597</v>
+        <v>771.8238</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         <v>4.232721494747124</v>
       </c>
       <c r="I4" t="n">
-        <v>775.0538</v>
+        <v>772.4913</v>
       </c>
     </row>
     <row r="5">
@@ -591,7 +591,7 @@
         <v>4.318108916503811</v>
       </c>
       <c r="I5" t="n">
-        <v>772.1958</v>
+        <v>772.8627</v>
       </c>
     </row>
   </sheetData>
